--- a/aircraft/reports/manufacturer/Cessna/aircraft-type-pie-chart.xlsx
+++ b/aircraft/reports/manufacturer/Cessna/aircraft-type-pie-chart.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4947,6 +4947,67 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>15538</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Abingdon</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Excellent Air</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ECA2JP</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>OXF</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>D-ISJP</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>525A-0030</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>525B Citation CJ3</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Cessna</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
